--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-06_requests_申請_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-06_requests_申請_テーブル詳細設計書.xlsx
@@ -288,6 +288,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -585,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C22"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -593,6 +596,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -607,6 +612,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -675,7 +682,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -715,12 +722,14 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち requests を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
-章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
+          <t>本書の位置づけ：KF-DD-003 は全 10 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち requests を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration の V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql（Flyway。KF-DD-003 v2.3 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）に、2026/10/05 のコード（AttendanceService / RequestService / ApprovalService / DepartmentController）から起こした ONL-024〜026（休憩・離席の開始・終了、部署一覧。番号は仮）と既存処理の追加アクセスを重ね、BAT-001〜003 と合わせて抽出した。
+章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications / attendance_breaks）のみ作成している。</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K28"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -759,6 +768,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -784,8 +794,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>代表的な 4 パターン：①山田の年休申請（承認待ち、1段目）、②鈴木の半休（承認済み）、③山田の打刻修正（差戻し）、④鈴木の下書き。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>代表的な 5 パターン：①山田の年休申請（承認待ち、1段目）、②鈴木の半休（承認済み）、③山田の打刻修正（差戻し）、④鈴木の下書き、⑤山田の休憩修正（下書き）。
+例の INSERT は V1〜V5 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → attendance_breaks → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -798,6 +808,7 @@
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="10" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -1100,34 +1111,71 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>3（山田）</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>NULL（corrected BREAK 12:00〜13:00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>8.3 INSERT 例（実際に実行できる SQL）</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
@@ -1138,15 +1186,15 @@
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="n"/>
     </row>
-    <row r="14" ht="48.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-10-14',DATE '2026-10-16','FULL',3.0,'私用のため','PENDING',1,TIMESTAMP '2026-10-02 09:30:00');</t>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -1162,12 +1210,12 @@
     <row r="15" ht="48.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='hanako@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-09-07',DATE '2026-09-07','AM',0.5,NULL,'APPROVED',2,TIMESTAMP '2026-09-01 10:00:00');</t>
+          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-10-14',DATE '2026-10-16','FULL',3.0,'私用のため','PENDING',1,TIMESTAMP '2026-10-02 09:30:00');</t>
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
@@ -1183,12 +1231,12 @@
     <row r="16" ht="48.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,corrected_clock_in,corrected_clock_out,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'CLOCK_CORRECTION',DATE '2026-09-30',DATE '2026-09-30',TIMESTAMP '2026-09-30 09:00:00',TIMESTAMP '2026-09-30 18:00:00','退勤打刻漏れ','RETURNED',1,TIMESTAMP '2026-10-01 09:10:00');</t>
+          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='hanako@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-09-07',DATE '2026-09-07','AM',0.5,NULL,'APPROVED',2,TIMESTAMP '2026-09-01 10:00:00');</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -1201,15 +1249,15 @@
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n"/>
     </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17" ht="48.5" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,status,current_step) VALUES ((SELECT id FROM users WHERE email='hanako@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-11-20',DATE '2026-11-20','FULL',1.0,'DRAFT',0);</t>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,corrected_clock_in,corrected_clock_out,reason,status,current_step,submitted_at) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'CLOCK_CORRECTION',DATE '2026-09-30',DATE '2026-09-30',TIMESTAMP '2026-09-30 09:00:00',TIMESTAMP '2026-09-30 18:00:00','退勤打刻漏れ','RETURNED',1,TIMESTAMP '2026-10-01 09:10:00');</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -1222,13 +1270,38 @@
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO requests(user_id,request_type,leave_type_id,start_date,end_date,unit,days,status,current_step) VALUES ((SELECT id FROM users WHERE email='hanako@example.com'),'LEAVE',(SELECT id FROM leave_types WHERE name='年次有給休暇'),DATE '2026-11-20',DATE '2026-11-20','FULL',1.0,'DRAFT',0);</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,corrected_break_kind,corrected_break_start,corrected_break_end,reason,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'BREAK_CORRECTION',DATE '2026-10-02',DATE '2026-10-02','BREAK',TIMESTAMP '2026-10-02 12:00:00',TIMESTAMP '2026-10-02 13:00:00','昼休みの打刻漏れ','DRAFT',0);</t>
+        </is>
+      </c>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
@@ -1239,78 +1312,38 @@
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="n"/>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>結果（SQLSTATE）</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>申請状態の値不正（ck_req_status）</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-01',DATE '2026-12-01','DONE',0);</t>
-        </is>
-      </c>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>23514 CHECK 制約違反</t>
-        </is>
-      </c>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
     </row>
-    <row r="22" ht="48.5" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>申請種別の値不正（ck_req_type）</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'OVERTIME',DATE '2026-12-01',DATE '2026-12-01','DRAFT',0);</t>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -1318,28 +1351,28 @@
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>23514 CHECK 制約違反</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>結果（SQLSTATE）</t>
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n"/>
     </row>
-    <row r="23" ht="48.5" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>current_step 未指定（NOT NULL・DEFAULT なし）</t>
+          <t>申請状態の値不正（ck_req_status）</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-01',DATE '2026-12-01','DRAFT');</t>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-01',DATE '2026-12-01','DONE',0);</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1349,7 +1382,7 @@
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>23502 NOT NULL 違反</t>
+          <t>23514 CHECK 制約違反</t>
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
@@ -1358,17 +1391,17 @@
     <row r="24" ht="48.5" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>終了日が開始日より前（現状は DB が止めない。課題 R-2）</t>
+          <t>申請種別の値不正（ck_req_type）</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-05',DATE '2026-12-01','DRAFT',0);</t>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'OVERTIME',DATE '2026-12-01',DATE '2026-12-01','DRAFT',0);</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -1378,106 +1411,197 @@
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>成功してしまう（DB は拒否しない＝課題。実行した場合は DELETE で元に戻すこと）</t>
+          <t>23514 CHECK 制約違反</t>
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
+    <row r="25" ht="48.5" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席種別の値不正（ck_req_break_kind）</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,corrected_break_kind,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'BREAK_CORRECTION',DATE '2026-12-01',DATE '2026-12-01','LUNCH','DRAFT',0);</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>23514 CHECK 制約違反</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="48.5" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>current_step 未指定（NOT NULL・DEFAULT なし）</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-01',DATE '2026-12-01','DRAFT');</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>23502 NOT NULL 違反</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n"/>
+    <row r="27" ht="48.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>終了日が開始日より前（現状は DB が止めない。課題 R-2）</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO requests(user_id,request_type,start_date,end_date,status,current_step) VALUES ((SELECT id FROM users WHERE email='taro@example.com'),'LEAVE',DATE '2026-12-05',DATE '2026-12-01','DRAFT',0);</t>
+        </is>
+      </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>成功してしまう（DB は拒否しない＝課題。実行した場合は DELETE で元に戻すこと）</t>
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="n"/>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>WITH u AS (UPDATE requests SET reason = reason WHERE id = (SELECT MIN(id) FROM requests) RETURNING created_at, updated_at) SELECT updated_at &gt; created_at AS trigger_worked FROM u;</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>trigger_worked = true（8章のデータを投入済みの DB で、INSERT と別トランザクションの場合）</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="10" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="28">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I28:K28"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B15:K15"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="B30:H30"/>
     <mergeCell ref="I24:K24"/>
+    <mergeCell ref="C27:H27"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="B16:K16"/>
-    <mergeCell ref="I20:K20"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="B18:K18"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I30:K30"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="B14:K14"/>
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="I27:K27"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="B19:K19"/>
+    <mergeCell ref="I25:K25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1491,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1626,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -1578,15 +1703,15 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="48.5" customHeight="1">
+    <row r="7" ht="63" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>バックアップ（BAT-003）</t>
+          <t>V5 の適用（既存データ・ロック）</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>V5 は requests に 3 列を NULL 可で追加し（既存行は NULL のまま）、ck_req_type を DROP して BREAK_CORRECTION を許す定義で ADD し直し、ck_req_break_kind を追加する。ADD CONSTRAINT は全行を検査するが、既存の request_type は LEAVE / CLOCK_CORRECTION のため違反しない。ALTER TABLE は ACCESS EXCLUSIVE ロックを取るが、年約 5,000 行の小さな表で短時間の見込み。BREAK_CORRECTION の申請が登録された後は、V5 を元に戻す（列・制約を DROP する）と該当申請が失われる／制約違反になるため、戻す場合は V6 以降で該当行の扱いを決めてから行う。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -1594,15 +1719,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48.5" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>マイグレーション</t>
+          <t>バックアップ（BAT-003）</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -1610,79 +1735,64 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="48.5" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>マイグレーション</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Flyway（V1__init_schema.sql：set_updated_at 関数・トリガ・初期データを含む／V2・V3：祝日の初期データ／V4：attendance_breaks の追加／V5：requests への休憩・離席修正の 3 列と制約の追加）＋ spring.jpa.hibernate.ddl-auto=validate。V1〜V5 は適用後に編集せず、列追加・索引追加は次の版 V6__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.2 既知課題・未決事項（未解決のもの。解消済みは 9.2b）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>推奨対応</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="77.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1860,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -1763,7 +1873,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1782,468 +1892,494 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="92" customHeight="1">
+    <row r="16" ht="106.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>C-7</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>保存期間 5 年を超えたデータの自動削除・アーカイブが未実装</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §9（決定 6）は勤怠・申請・監査ログの保存期間を 5 年（設定値）とし、BAT-005『監査ログ／履歴の保存期間管理（アーカイブ）』を計画している。現行の backend には削除・アーカイブ処理も保存期間の設定値も無く、業務データは物理削除しない（例外は通知・祝日・再提出時の承認ステップ）。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始から 5 年間は影響しない。5 年を超えた後の扱い（残す／消す・退避）の手順が無く、運用者の判断になる。件数は 5 年で 5 表合計（attendance_breaks 約 75 万行を含む）約 120 万行規模で、容量・性能上の問題にはなりにくい。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>運用開始（2026 年）の 5 年後（2031 年）までに、BAT-005 の設計・実装、または手動の退避 SQL の手順を決める。それまでは『消さずに保持する』方針で運用する（5 年はこの方針の目安）。</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="121" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>R-2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>requests の CHECK 不足（期間・段・種別別必須列）</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、BREAK_CORRECTION 時の corrected_break_kind/start/end 必須（開始＜終了・対象日と同じ日付）、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>手動投入・将来の別入口で矛盾した申請が入る。</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind を追加（本書 3章の推奨 DDL）。</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind / ck_req_break_range を追加（本書 3章の推奨 DDL）。</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="63" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>R-3</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>取下げ・差戻し等の実行日時・実行者を専用列に残せない</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>updated_at はトリガで信頼できるが、取下げ以外の更新でも更新されるため『取下げ日時』とは断定できない。取下げ者は申請者本人のみのため不要だが、承認履歴は approval_steps にのみ存在する。</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>取下げ日時を厳密に出せない（最終更新日時で代用）。</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>必要なら withdrawn_at 列を追加。</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>R-4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>楽観ロック用 version 列が無い</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>@Version を使えず、requests 行の SELECT ... FOR UPDATE ＋ 状態条件付き UPDATE で排他している（ONL-010 決定事項）。</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>現方式で二重承認は防げるが、ロック待ちが発生する。他の更新経路（管理画面等）が増えると漏れやすい。</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>当面は現方式を維持。更新経路が増える時点で version BIGINT NOT NULL DEFAULT 0 を追加。</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="77.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20" ht="77.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>R-5</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>集計用の索引が無い</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ONL-018/020 の requests サブクエリは request_type='LEAVE' AND status='APPROVED' AND start_date BETWEEN（user_id 指定なし）で、user_id 先頭の idx_req_* が使えず全件走査（年 5,000 行までは問題なし）。</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>数年分で月次集計が遅くなる可能性。</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>必要になった時点で (status, start_date) の部分索引を追加。</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>R-6</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>承認待ちのまま止まる申請が発生しうる。</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
         </is>
       </c>
     </row>
     <row r="21" ht="63" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
+          <t>R-6</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>承認待ちのまま止まる申請が発生しうる。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="63" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>R-7</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>下書き・差戻しの内容を更新する API が無い</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>ONL-022 は提出（再提出）のみで、下書きの内容更新（PUT）は未定義。RETURNED の申請も内容を修正できず、直したい場合は取り下げて新規申請になる。</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>差戻しの目的（修正して再提出）を画面で果たせない。</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>更新 API（PUT /api/requests/{id}）の追加（DRAFT / RETURNED のみ可）。</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="77.5" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23" ht="121" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>AS-1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。API の応答（ONL-007 の承認履歴）は、PENDING でない申請の WAITING を SKIPPED（処理なし）と表示するが、これは RequestService#displayStatus の表示変換で DB の値は WAITING のまま。</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>方針を明文化（現行の維持）。もしくは終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>方針を明文化（現行の維持。画面上の誤解は SKIPPED 表示で緩和済み）。DB 側でも区別したい場合は、終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="92" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>AS-3</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="106.5" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28" ht="106.5" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>V1 の全 9 表（V4 の attendance_breaks にも同様）に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="92" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29" ht="135.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="92" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30" ht="135.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="92" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>R-1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>下書き提出・差戻し後の再提出を行う ONL が存在しない</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>ONL-022（POST /api/requests/{id}/submit）を追加。DRAFT / RETURNED → PENDING。ONL-005 と同じ検証（E-004 / E-005）、LEAVE は days を再計算、旧 approval_steps を全て削除して作り直す（uq(request_id, step_no) 対策にバルク DELETE）、現在の承認者へ REQUEST_SUBMITTED 通知。</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>下書きの内容を更新する API（課題 R-7）と、再提出で承認履歴が消える点（課題 AS-3）が残る。</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>requests, approval_steps</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
-        </is>
-      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="10" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>ONL-006</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>件数が多いユーザーでも全件を返す（ページングなし）。他の画面からの遷移用に requestType / status 以外の絞込（期間など）は提供しない。</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -2253,7 +2389,7 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2263,17 +2399,17 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="10" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-006</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2283,7 +2419,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
+          <t>件数が多いユーザーでも全件を返す（ページングなし）。他の画面からの遷移用に requestType / status 以外の絞込（期間など）は提供しない。</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -2293,17 +2429,17 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（今後）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
         </is>
       </c>
       <c r="D37" s="9" t="n"/>
@@ -2313,7 +2449,7 @@
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2323,53 +2459,94 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
+          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="10" t="n"/>
     </row>
-    <row r="39" ht="48.5" customHeight="1">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>既知の制約</t>
+          <t>既知の制約（今後）</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="10" t="n"/>
     </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>ONL-013</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="48.5" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="C37:F37"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C37:F37"/>
     <mergeCell ref="C36:F36"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2383,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2394,6 +2571,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -2467,12 +2645,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SELECT r.id, r.status, r.current_step, COUNT(s.id) AS steps FROM requests r LEFT JOIN approval_steps s ON s.request_id = r.id WHERE r.status &lt;&gt; 'DRAFT' GROUP BY r.id, r.status, r.current_step HAVING COUNT(s.id) &lt;&gt; 2;</t>
+          <t>SELECT r.id, r.status, r.current_step, COUNT(s.id) AS steps FROM requests r LEFT JOIN approval_steps s ON s.request_id = r.id WHERE r.status &lt;&gt; 'DRAFT' GROUP BY r.id, r.status, r.current_step HAVING COUNT(s.id) NOT IN (1, 2) OR (COUNT(s.id) = 1 AND MIN(s.step_no) &lt;&gt; 2);</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>0 行（提出時に必ず 2 行作る）</t>
+          <t>0 行（提出時に 2 行を作る。上長なし・無効の申請は 2段目のみの 1 行）</t>
         </is>
       </c>
       <c r="E5" s="9" t="n"/>
@@ -2502,7 +2680,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="63" customHeight="1">
+    <row r="7" ht="92" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -2515,7 +2693,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, request_type, status FROM requests WHERE status &lt;&gt; 'DRAFT' AND ((request_type='LEAVE' AND (leave_type_id IS NULL OR unit IS NULL OR days IS NULL)) OR (request_type='CLOCK_CORRECTION' AND (corrected_clock_in IS NULL OR corrected_clock_out IS NULL)));</t>
+          <t>SELECT id, request_type, status FROM requests WHERE status &lt;&gt; 'DRAFT' AND ((request_type='LEAVE' AND (leave_type_id IS NULL OR unit IS NULL OR days IS NULL)) OR (request_type='CLOCK_CORRECTION' AND (corrected_clock_in IS NULL OR corrected_clock_out IS NULL)) OR (request_type='BREAK_CORRECTION' AND (corrected_break_kind IS NULL OR corrected_break_start IS NULL OR corrected_break_end IS NULL)));</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2526,7 +2704,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>5</t>
@@ -2534,23 +2712,23 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>期間逆転・日数不正</t>
+          <t>休憩・離席修正の時刻の不整合（終了≦開始・対象日と別の日付）</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, start_date, end_date, days FROM requests WHERE end_date &lt; start_date OR days &lt;= 0;</t>
+          <t>SELECT id, start_date, corrected_break_start, corrected_break_end FROM requests WHERE request_type = 'BREAK_CORRECTION' AND (corrected_break_end &lt;= corrected_break_start OR corrected_break_start::date &lt;&gt; start_date OR corrected_break_end::date &lt;&gt; start_date);</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>0 行（上記の異常系例を実行した場合は 1 行）</t>
+          <t>0 行（課題 R-2：ck_req_break_range 追加前の事前確認）</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="77.5" customHeight="1">
+    <row r="9" ht="48.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -2558,23 +2736,23 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>同一ユーザーの有効な休暇の期間重複（PENDING/APPROVED）</t>
+          <t>休憩・離席の列が別の種別に入っている</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SELECT a.id AS id_a, b.id AS id_b, a.user_id FROM requests a JOIN requests b ON a.user_id = b.user_id AND a.id &lt; b.id AND a.request_type='LEAVE' AND b.request_type='LEAVE' AND a.status IN ('PENDING','APPROVED') AND b.status IN ('PENDING','APPROVED') AND a.start_date &lt;= b.end_date AND a.end_date &gt;= b.start_date;</t>
+          <t>SELECT id, request_type FROM requests WHERE request_type &lt;&gt; 'BREAK_CORRECTION' AND (corrected_break_kind IS NOT NULL OR corrected_break_start IS NOT NULL OR corrected_break_end IS NOT NULL);</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>0 行（ONL-005 の E-005 チェックが機能している）</t>
+          <t>0 行（BREAK_CORRECTION 以外では NULL のはず）</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="77.5" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -2582,23 +2760,23 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>承認者が無効・上長でなくなった承認待ち（課題 R-6）</t>
+          <t>期間逆転・日数不正</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SELECT r.id, s.step_no, u.email, u.status, u.role FROM requests r JOIN approval_steps s ON s.request_id = r.id AND s.step_no = r.current_step JOIN users u ON u.id = s.approver_id WHERE r.status='PENDING' AND s.status='WAITING' AND (u.status &lt;&gt; 'ACTIVE' OR u.role = 'EMPLOYEE');</t>
+          <t>SELECT id, start_date, end_date, days FROM requests WHERE end_date &lt; start_date OR days &lt;= 0;</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>0 行（あれば承認者付替えが必要）</t>
+          <t>0 行（上記の異常系例を実行した場合は 1 行）</t>
         </is>
       </c>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="48.5" customHeight="1">
+    <row r="11" ht="77.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>8</t>
@@ -2606,23 +2784,23 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>提出から 7 日以上滞留している承認待ち</t>
+          <t>同一ユーザーの有効な休暇の期間重複（PENDING/APPROVED）</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, user_id, current_step, submitted_at FROM requests WHERE status='PENDING' AND submitted_at &lt; CURRENT_TIMESTAMP - INTERVAL '7 days' ORDER BY submitted_at;</t>
+          <t>SELECT a.id AS id_a, b.id AS id_b, a.user_id FROM requests a JOIN requests b ON a.user_id = b.user_id AND a.id &lt; b.id AND a.request_type='LEAVE' AND b.request_type='LEAVE' AND a.status IN ('PENDING','APPROVED') AND b.status IN ('PENDING','APPROVED') AND a.start_date &lt;= b.end_date AND a.end_date &gt;= b.start_date;</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>催促対象</t>
+          <t>0 行（ONL-005 の E-005 チェックが機能している）</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="77.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>9</t>
@@ -2630,40 +2808,89 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>updated_at トリガ trg_requests_updated_at が存在し有効であること</t>
+          <t>承認者が無効・上長でなくなった承認待ち（課題 R-6）</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'requests'::regclass AND NOT tgisinternal;</t>
+          <t>SELECT r.id, s.step_no, u.email, u.status, u.role FROM requests r JOIN approval_steps s ON s.request_id = r.id AND s.step_no = r.current_step JOIN users u ON u.id = s.approver_id WHERE r.status='PENDING' AND s.status='WAITING' AND (u.status &lt;&gt; 'ACTIVE' OR u.role = 'EMPLOYEE');</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 行（trg_requests_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+          <t>0 行（あれば承認者付替えが必要）</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="48.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>提出から 7 日以上滞留している承認待ち</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SELECT id, user_id, current_step, submitted_at FROM requests WHERE status='PENDING' AND submitted_at &lt; CURRENT_TIMESTAMP - INTERVAL '7 days' ORDER BY submitted_at;</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>催促対象</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>updated_at トリガ trg_requests_updated_at が存在し有効であること</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'requests'::regclass AND NOT tgisinternal;</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 行（trg_requests_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>全 SQL を PostgreSQL 16 上で V1〜V5 のマイグレーション（V1 は v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
@@ -2671,6 +2898,7 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2685,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2722,7 +2950,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1">
+    <row r="2" ht="68" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -2744,6 +2972,52 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2 追加に伴いデータ例の前提を更新。保存期間 5 年の自動削除・アーカイブは未実装であることを課題 C-7 として追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="233" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>コード（V5 マイグレーション、Request Entity、RequestService / ApprovalService / AttendanceService）と突合して更新。①V5 で追加した休憩・離席修正申請（request_type = BREAK_CORRECTION）に対応：列 corrected_break_kind / corrected_break_start / corrected_break_end（3 列。NULL 可。物理列順は updated_at の後ろ）、制約 ck_req_type（BREAK_CORRECTION を許可。V1 の定義を DROP→ADD）と ck_req_break_kind を追加②4章に 4.4（申請種別と使用列）・4.5（BREAK_CORRECTION の検証。E-002 / E-003 / E-005）を追加し、最終承認の反映を更新③承認ルートの記述を訂正（上長なし・無効の場合 approval_steps は 2段目のみの 1 行。従来『2 行を必ず作成』と記載）④8章のデータ例に申請 5（山田の休憩・離席修正。下書き）、10章の確認 SQL に BREAK_CORRECTION の必須列・時刻整合・列の混入チェックを追加⑤3.4 の推奨 DDL（ck_req_kind）を BREAK_CORRECTION 対応に更新し ck_req_break_range を追加⑥課題 R-2 を更新、運用に V5 適用時の注意を追記。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2758,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2769,6 +3043,7 @@
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -2805,7 +3080,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>休暇申請（LEAVE）と打刻修正申請（CLOCK_CORRECTION）を 1 テーブルで管理する申請ヘッダ。状態（status）と現在の承認段（current_step）を持ち、承認の各段は approval_steps に分けて持つ。作成（ONL-005）・提出/再提出（ONL-022）・一覧（ONL-006）・詳細（ONL-007）・取下げ（ONL-008）・承認/差戻し/却下（ONL-010〜012）・月次集計（ONL-018/020）・年 5 日取得判定（ONL-013）の中心。</t>
+          <t>休暇申請（LEAVE）・打刻修正申請（CLOCK_CORRECTION）・休憩・離席修正申請（BREAK_CORRECTION。V5 で追加）を 1 テーブルで管理する申請ヘッダ。状態（status）と現在の承認段（current_step）を持ち、承認の各段は approval_steps に分けて持つ。作成（ONL-005）・提出/再提出（ONL-022）・一覧（ONL-006）・詳細（ONL-007）・取下げ（ONL-008）・承認/差戻し/却下（ONL-010〜012）・月次集計（ONL-018/020）・年 5 日取得判定（ONL-013）の中心。</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -2813,7 +3088,7 @@
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>DBMS・文字コード</t>
@@ -2821,7 +3096,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway のマイグレーション（backend/src/main/resources/db/migration の V1__init_schema.sql（V5__break_correction_request.sql で列・制約を追加））。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -2933,7 +3208,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>列 16 / 制約 6（PK 1・FK 2・UNIQUE 0・CHECK 3）/ 追加索引 2</t>
+          <t>列 19 / 制約 7（PK 1・FK 2・UNIQUE 0・CHECK 4）/ 追加索引 2</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2965,7 +3240,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.RequestRepository（findByIdForUpdate / sumPendingLeaveDays / findOverlappingLeaves / findAllByUser(AndStatus) / advanceStepIfPending / updateStatusIfPending / sumApprovedLeaveDays ほか）</t>
+          <t>repository.RequestRepository（findByIdForUpdate / sumPendingLeaveDays / findOverlappingLeaves / findAllByUser(AndStatus) / advanceStepIfPending / updateStatusIfPending / sumApprovedLeaveDays / existsByUserIdAndRequestTypeAndStartDateAndStatus ほか）</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -2973,6 +3248,7 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -3357,6 +3633,7 @@
       </c>
       <c r="F31" s="10" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
@@ -3462,7 +3739,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>ONL-001〜022 の概要（ONL-023 以降は個別のオンライン詳細設計書）</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -3509,10 +3786,10 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
+    <row r="41" ht="106.5" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3522,7 +3799,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>本書の自動生成元（V2・V3 は祝日の初期データのみ）</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -3582,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:M20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3600,10 +3877,11 @@
     <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（db/migration の V1・V4・V5 から自動生成。物理列順）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3812,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="92" customHeight="1">
+    <row r="6" ht="135.5" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
@@ -3851,17 +4129,18 @@
         <is>
           <t>LEAVE：休暇申請
 CLOCK_CORRECTION：打刻修正申請
-CHECK ck_req_type: request_type IN ('LEAVE','CLOCK_CORRECTION')</t>
+BREAK_CORRECTION：休憩・離席修正申請
+CHECK ck_req_type: request_type IN ('LEAVE','CLOCK_CORRECTION','BREAK_CORRECTION')</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>申請種別。LEAVE（休暇申請）／CLOCK_CORRECTION（打刻修正申請）。</t>
+          <t>申請種別。LEAVE（休暇申請）／CLOCK_CORRECTION（打刻修正申請）／BREAK_CORRECTION（休憩・離席修正申請。V5 で追加）。</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>ONL-005 の requestType（LEAVE / CLOCK_CORRECTION）。</t>
+          <t>ONL-005 の requestType（LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION。DTO の @Pattern と ck_req_type で検証）。</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -3979,12 +4258,12 @@
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>開始日。打刻修正申請では対象日。</t>
+          <t>開始日。打刻修正・休憩離席修正申請では対象日。</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>ONL-005。休暇は開始日、打刻修正は対象日。承認時の打刻反映日・休暇の利用日にも使う（ONL-010）。</t>
+          <t>ONL-005。休暇は開始日、打刻修正・休憩離席修正は対象日。承認時の打刻・休憩離席の反映日・休暇の利用日にも使う（ONL-010）。</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -4037,12 +4316,12 @@
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>終了日。打刻修正申請では開始日と同じ。</t>
+          <t>終了日。打刻修正・休憩離席修正申請では開始日と同じ。</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>ONL-005。打刻修正は start_date と同日。</t>
+          <t>ONL-005。打刻修正・休憩離席修正は start_date と同日。</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -4338,12 +4617,12 @@
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>申請理由（最大200文字）。</t>
+          <t>申請理由（最大200文字）。提出時の打刻修正・休憩離席修正は必須、休暇は任意。</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>ONL-005（最大 200 文字。提出時の打刻修正は必須、休暇は任意）。通知本文・ログには出さない。</t>
+          <t>ONL-005（最大 200 文字。提出時の打刻修正・休憩離席修正は必須、休暇は任意）。通知本文・ログには出さない。</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -4655,29 +4934,212 @@
       </c>
       <c r="M19" s="12" t="inlineStr"/>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="10" t="n"/>
+    <row r="20" ht="106.5" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>修正後の休憩・離席種別</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>corrected_break_kind</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>BREAK：休憩
+AWAY：日中離席
+CHECK ck_req_break_kind: corrected_break_kind IS NULL OR corrected_break_kind IN ('BREAK','AWAY')</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>修正する区間の種別（休憩・離席修正申請のみ）。BREAK＝休憩、AWAY＝日中離席。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正のみ ONL-005 の breakKind（BREAK / AWAY）。最終承認時に attendance_breaks.kind へ反映（ONL-010）。他の申請種別は NULL。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakKind
+String</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>V5__break_correction_request.sql で追加（ALTER TABLE ADD COLUMN のため物理列順は updated_at の後ろ。Entity では corrected_clock_out の後ろに定義）
+使用ONL: 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="92" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>修正後の休憩・離席開始日時</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>corrected_break_start</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>秒未満6桁</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>修正後の区間の開始日時（休憩・離席修正申請のみ。対象日＋入力 HH:mm の JST 日時）。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正のみ ONL-005（対象日＋入力 breakStart HH:mm の JST 日時）。承認時に attendance_breaks.start_at へ反映。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakStart
+LocalDateTime</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>V5__break_correction_request.sql で追加（ALTER TABLE ADD COLUMN のため物理列順は updated_at の後ろ。Entity では corrected_clock_out の後ろに定義）
+使用ONL: 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="92" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>修正後の休憩・離席終了日時</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>corrected_break_end</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>秒未満6桁</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>修正後の区間の終了日時（休憩・離席修正申請のみ）。開始より後。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>同上（breakEnd。attendance_breaks.end_at へ反映）。開始より後であること（ONL-005 の E-003）。V5 で追加。</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakEnd
+LocalDateTime</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>V5__break_correction_request.sql で追加（ALTER TABLE ADD COLUMN のため物理列順は updated_at の後ろ。Entity では corrected_clock_out の後ろに定義）
+使用ONL: 005</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値はマイグレーション（V1・V4・V5）の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A20:M20"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A23:M23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4691,7 +5153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4702,10 +5164,11 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（マイグレーションの定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4826,7 +5289,7 @@
       </c>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="48.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>CHECK</t>
@@ -4834,13 +5297,13 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>ck_req_type</t>
+          <t>ck_req_status</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>request_type IN ('LEAVE','CLOCK_CORRECTION')</t>
+          <t>status IN ('DRAFT','PENDING','RETURNED','REJECTED','APPROVED','WITHDRAWN')</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -4850,7 +5313,7 @@
       </c>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="48.5" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CHECK</t>
@@ -4858,18 +5321,18 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>ck_req_status</t>
+          <t>ck_req_unit</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>status IN ('DRAFT','PENDING','RETURNED','REJECTED','APPROVED','WITHDRAWN')</t>
+          <t>unit IS NULL OR unit IN ('FULL','AM','PM')</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>コード値の制限</t>
+          <t>コード値の制限。NULL は CHECK を通過する（NOT NULL ではない）</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
@@ -4882,18 +5345,18 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>ck_req_unit</t>
+          <t>ck_req_type</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr"/>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>unit IS NULL OR unit IN ('FULL','AM','PM')</t>
+          <t>request_type IN ('LEAVE','CLOCK_CORRECTION','BREAK_CORRECTION')</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>コード値の制限。NULL は CHECK を通過する（NOT NULL ではない）</t>
+          <t>コード値の制限。V5 で追加（V1 の同名制約を DROP して再作成し、BREAK_CORRECTION を許可）</t>
         </is>
       </c>
       <c r="F9" s="10" t="n"/>
@@ -4901,158 +5364,183 @@
     <row r="10" ht="48.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>ck_req_break_kind</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>corrected_break_kind IS NULL OR corrected_break_kind IN ('BREAK','AWAY')</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>コード値の制限。NULL は CHECK を通過する（NOT NULL ではない）。V5 で追加</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="48.5" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>TRIGGER</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>trg_requests_updated_at</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>BEFORE UPDATE ON requests FOR EACH ROW EXECUTE FUNCTION set_updated_at()</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>UPDATE のたびに NEW.updated_at = CURRENT_TIMESTAMP（トランザクション開始時刻）。値が変わらない UPDATE・updated_at を明示した UPDATE でも上書きする。INSERT では動かない（DEFAULT）。</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="92" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="92" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>（列制約）</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>user_id, request_type, start_date, end_date, status, current_step, created_at, updated_at</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>列定義（2章）参照</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="63" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>DEFAULT</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>（列既定値）</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>created_at=CURRENT_TIMESTAMP; updated_at=CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>DEFAULT</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>列定義（2章）参照</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>3.2 インデックス一覧と、使用する実クエリ（ONL 規格の SQL との対応）</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="48.5" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="48.5" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>索引名</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>列（順序）</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>作成元</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>使用する実クエリ（ONL / BAT の SQL。△＝OR・任意条件のため実際は効かない可能性。PK／一意キーで絞れるクエリは PK が優先される）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="193.5" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17" ht="193.5" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>requests_pkey</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PRIMARY KEY（自動作成）</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>PRIMARY KEY 制約が自動作成（名前は PostgreSQL の自動命名）</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>PK 検索・行ロック（findById / findByIdForUpdate）、UPDATE ... WHERE id = ?</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>○ ONL-005 current_step の更新  [先頭 1/1 列で絞込]  WHERE id = ?
 ○ ONL-007 申請の取得  [先頭 1/1 列で絞込]  WHERE id = ?
@@ -5063,33 +5551,33 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="409" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="18" ht="409" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>idx_req_user</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>通常（btree）</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>user_id, status</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>CREATE INDEX（schema.sql）</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ユーザー別の一覧・引当集計（user_id [+ status]）</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>○ ONL-005 承認待ち引当日数  [先頭 2/2 列で絞込]  WHERE user_id = ? AND request_type = 'LEAVE' AND leave_type_id = ? AND status = 'PENDING'
 ○ ONL-005 休暇の期間重複  [先頭 2/2 列で絞込]  WHERE user_id = ? AND request_type = 'LEAVE' AND status IN ('PENDING','APPROVED') AND start_date
@@ -5104,33 +5592,33 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="409" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="19" ht="409" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>idx_req_period</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>通常（btree）</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>user_id, start_date, end_date</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>CREATE INDEX（schema.sql）</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>ユーザー別の期間重複・期間集計（user_id, start_date, end_date）</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>○ ONL-005 承認待ち引当日数  [先頭 1/3 列で絞込]  WHERE user_id = ? AND request_type = 'LEAVE' AND leave_type_id = ? AND status = 'PENDING'
 ○ ONL-005 休暇の期間重複  [先頭 1/3 列で絞込]  WHERE user_id = ? AND request_type = 'LEAVE' AND status IN ('PENDING','APPROVED') AND start_date
@@ -5145,44 +5633,29 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>3.3 不足・過剰なインデックスの考察と推奨</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>索引</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>評価・考察</t>
-        </is>
-      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>総合評価</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>索引</t>
         </is>
       </c>
       <c r="B22" s="10" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>不足なし（user_id 起点の検索は idx_req_user / idx_req_period で足りる）。管理者向け集計用の部分索引はデータ増加後（課題 R-5）。</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>評価・考察</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -5192,13 +5665,13 @@
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>requests_pkey</t>
+          <t>総合評価</t>
         </is>
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>【適正】 ONL-007/008/010〜012 の主な入口。承認系は FOR UPDATE。</t>
+          <t>不足なし（user_id 起点の検索は idx_req_user / idx_req_period で足りる）。管理者向け集計用の部分索引はデータ増加後（課題 R-5）。</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -5208,165 +5681,206 @@
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>idx_req_user</t>
+          <t>requests_pkey</t>
         </is>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>【適正】 ONL-006 の一覧（user_id = ? [AND status = ?]。ソートはメモリ）、ONL-005/022 sumPendingLeaveDays（user_id, status='PENDING' を使用）。1 ユーザー 年 15 件のため十分。</t>
+          <t>【適正】 ONL-007/008/010〜012 の主な入口。承認系は FOR UPDATE。</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="34" customHeight="1">
+    <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>idx_req_period</t>
+          <t>idx_req_user</t>
         </is>
       </c>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>【適正】 ONL-005 findOverlappingLeaves（start_date &lt;= ? AND end_date &gt;= ?）、ONL-013 sumApprovedLeaveDays（start_date BETWEEN）。end_date は範囲条件の後ろ列で絞込には寄与しないが、1 ユーザー分に限られるため問題なし。</t>
+          <t>【適正】 ONL-006 の一覧（user_id = ? [AND status = ?]。ソートはメモリ）、ONL-005/022 sumPendingLeaveDays（user_id, status='PENDING' を使用）。1 ユーザー 年 15 件のため十分。</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>idx_req_period</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>【適正】 ONL-005 findOverlappingLeaves（start_date &lt;= ? AND end_date &gt;= ?）、ONL-013 sumApprovedLeaveDays（start_date BETWEEN）。end_date は範囲条件の後ろ列で絞込には寄与しないが、1 ユーザー分に限られるため問題なし。</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>3.4 推奨する変更（適用済みのマイグレーションは変更しない。提案のみ。DDL は V1〜V5＋8章データに対して実行確認済み）</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>提案</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>DDL（PostgreSQL）</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="63" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>期間・段・日数の整合 CHECK（課題 R-2）</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>ALTER TABLE requests ADD CONSTRAINT ck_req_period CHECK (start_date &lt;= end_date);
 ALTER TABLE requests ADD CONSTRAINT ck_req_step CHECK (current_step BETWEEN 0 AND 2);
 ALTER TABLE requests ADD CONSTRAINT ck_req_days CHECK (days IS NULL OR days &gt; 0);</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="92" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>種別別の必須列（課題 R-2）</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>ALTER TABLE requests ADD CONSTRAINT ck_req_kind CHECK ((request_type='LEAVE' AND leave_type_id IS NOT NULL AND unit IS NOT NULL AND days IS NOT NULL) OR (request_type='CLOCK_CORRECTION' AND corrected_clock_in IS NOT NULL AND corrected_clock_out IS NOT NULL) OR status='DRAFT');</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>（データ増加後）月次集計用（課題 R-5）</t>
+          <t>種別別の必須列（課題 R-2）</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="12" t="inlineStr">
         <is>
+          <t>ALTER TABLE requests ADD CONSTRAINT ck_req_kind CHECK ((request_type='LEAVE' AND leave_type_id IS NOT NULL AND unit IS NOT NULL AND days IS NOT NULL) OR (request_type='CLOCK_CORRECTION' AND corrected_clock_in IS NOT NULL AND corrected_clock_out IS NOT NULL) OR (request_type='BREAK_CORRECTION' AND corrected_break_kind IS NOT NULL AND corrected_break_start IS NOT NULL AND corrected_break_end IS NOT NULL) OR status='DRAFT');</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の時刻の整合（課題 R-2）</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>ALTER TABLE requests ADD CONSTRAINT ck_req_break_range CHECK (corrected_break_start IS NULL OR corrected_break_end IS NULL OR (corrected_break_end &gt; corrected_break_start AND corrected_break_start::date = start_date AND corrected_break_end::date = start_date));</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>（データ増加後）月次集計用（課題 R-5）</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
           <t>CREATE INDEX idx_req_leave_approved ON requests (start_date) WHERE request_type='LEAVE' AND status='APPROVED';</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="40">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C31:D31"/>
     <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
@@ -5382,7 +5896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F57"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5393,6 +5907,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -5405,6 +5920,36 @@
       <c r="E2" s="9" t="n"/>
       <c r="F2" s="10" t="n"/>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
@@ -5641,6 +6186,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
@@ -5709,7 +6255,7 @@
       </c>
       <c r="F44" s="10" t="n"/>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="48.5" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>（新規）</t>
@@ -5732,7 +6278,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>current_step=1（上長あり）／2（上長なし）、submitted_at=現在日時。approval_steps を2行 INSERT、現在の承認者へ通知</t>
+          <t>current_step=1（上長あり）／2（上長なし）、submitted_at=現在日時。approval_steps を INSERT（上長ありは 2 行、上長なし・無効は 2段目のみの 1 行）、現在の承認者へ通知</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -5765,7 +6311,7 @@
       </c>
       <c r="F46" s="10" t="n"/>
     </row>
-    <row r="47" ht="48.5" customHeight="1">
+    <row r="47" ht="77.5" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>PENDING（2段目）</t>
@@ -5788,7 +6334,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>UPDATE ... SET status='APPROVED' WHERE ... AND current_step=2。休暇なら leave_balances を FIFO 消化、打刻修正なら attendance_records へ反映</t>
+          <t>UPDATE ... SET status='APPROVED' WHERE ... AND current_step=2。休暇なら leave_balances を FIFO 消化、打刻修正なら attendance_records へ反映（その日の休憩・離席を考慮して勤務・残業を再計算）、休憩・離席修正なら attendance_breaks へ追加・修正（退勤済みなら勤務・残業を再計算）</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -5877,7 +6423,7 @@
       </c>
       <c r="F50" s="10" t="n"/>
     </row>
-    <row r="51" ht="92" customHeight="1">
+    <row r="51" ht="106.5" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>DRAFT / RETURNED</t>
@@ -5900,11 +6446,12 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>本人のみ。users→requests の順に FOR UPDATE。ONL-005 の提出時と同じ検証（LEAVE は days を再計算、E-004 残日数・E-005 期間重複）。status=PENDING、current_step=1（上長なしは 2）、submitted_at=現在日時、旧 approval_steps を全て DELETE して 2 行 INSERT し直す（差戻しコメント等の旧履歴は失われる。課題 AS-3）。現在の承認者へ REQUEST_SUBMITTED 通知。DRAFT/RETURNED 以外は E-016</t>
+          <t>本人のみ。users→requests の順に FOR UPDATE。ONL-005 の提出時と同じ検証（LEAVE は days を再計算、E-004 残日数・E-005 期間重複）。status=PENDING、current_step=1（上長なしは 2）、submitted_at=現在日時、旧 approval_steps を全て DELETE して INSERT し直す（上長ありは 2 行、上長なしは 2段目のみの 1 行）（差戻しコメント等の旧履歴は失われる。課題 AS-3）。現在の承認者へ REQUEST_SUBMITTED 通知。DRAFT/RETURNED 以外は E-016</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
@@ -6007,31 +6554,437 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>step 1=APPROVED（上長なしの場合は WAITING のまま）、step 2=WAITING</t>
+          <t>step 1=APPROVED（上長なし・無効の場合は 1段目の行自体が無い）、step 2=WAITING</t>
         </is>
       </c>
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="10" t="n"/>
     </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>4.4 request_type（申請種別）と種別別の使用列</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>コード</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>使う列</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>start_date / end_date</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>最終承認での反映（ONL-010）</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>承認ルート</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>LEAVE</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>休暇申請</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>leave_type_id・unit・days（reason は任意）</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>開始日／終了日（期間）</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>leave_balances を FIFO で消化（UNLIMITED 種別は何もしない）</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>1段目 上長 → 2段目 管理者（上長なしは 2段目のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48.5" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>CLOCK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>打刻修正申請</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>corrected_clock_in・corrected_clock_out（reason 必須）</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>対象日（end_date＝start_date）</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>attendance_records の出退勤を上書き（行が無ければ INSERT）。その日の休憩・離席を考慮して勤務・残業を再計算</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48.5" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（V5 で追加）</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>corrected_break_kind・corrected_break_start・corrected_break_end（reason 必須）</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>対象日（end_date＝start_date）</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks へ区間を追加（同種別の継続中の区間があればそれを修正）。退勤済みなら勤務・残業を再計算</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>4.5 BREAK_CORRECTION の検証（提出時 ONL-005/022 と最終承認時 ONL-010 の両方。AttendanceService#checkBreakCorrection ほか）</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>メッセージ（HTTP）</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="10" t="n"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>種別が BREAK / AWAY 以外（DTO の @Pattern）</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の種別が正しくありません。（400）</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="10" t="n"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>種別・開始・終了のいずれかが未入力</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の種別は必須入力です。／開始時刻は必須入力です。／終了時刻は必須入力です。（400）</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="10" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>対象日が本日より後</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>対象日は本日以前の日付を指定してください。（400）</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="10" t="n"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>終了が開始以前（入力時・検証時）</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>終了時刻は開始時刻より後の時刻を指定してください。（400）</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>理由が空（提出時のみ。下書きは任意）</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>E-002</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>理由は必須入力です。（400）</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="10" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>対象日に出勤打刻が無い</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>対象日に出勤打刻がないため、休憩・離席を修正できません。（400）</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="10" t="n"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>開始が出勤より前、または終了が退勤より後</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の時刻は出勤 HH:mm 以降（退勤済みは 出勤 HH:mm〜退勤 HH:mm）の範囲内で指定してください。（400）</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="10" t="n"/>
+    </row>
+    <row r="74" ht="48.5" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>他の区間と時間帯が重なる（修正対象の継続中の同種別区間は除く）</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>E-005</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>他の休憩・離席の時間帯と重なっています。（409）</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="10" t="n"/>
+    </row>
+    <row r="75" ht="77.5" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>同一対象日・同一申請種別（BREAK_CORRECTION）の PENDING が既にある（提出時のみ。種別 BREAK/AWAY は問わない）</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>E-005</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>同一期間に既に申請があります。（409）</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="29">
     <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="D72:F72"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="E50:F50"/>
     <mergeCell ref="E51:F51"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="D67:F67"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="E49:F49"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D56:F56"/>
     <mergeCell ref="E45:F45"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="D57:F57"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6046,7 +6999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6057,6 +7010,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -6165,6 +7119,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
@@ -6265,6 +7220,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -6293,6 +7249,7 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -6313,7 +7270,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>親：users（user_id＝申請者、必須）、leave_types（leave_type_id、NULL 可）。子：approval_steps.request_id（0..2）、notifications.request_id（0..*、NULL 可＝申請に紐づかない通知）。</t>
+          <t>親：users（user_id＝申請者、必須）、leave_types（leave_type_id、NULL 可）。子：approval_steps.request_id（0..2）、notifications.request_id（0..*、NULL 可＝申請に紐づかない通知）。attendance_breaks との FK は無い（BREAK_CORRECTION は最終承認で対象日の attendance_breaks を直接更新する）。</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -6345,7 +7302,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>整合性をアプリで守る点：(1) 種別別の必須項目（LEAVE: leave_type_id/unit/days、CLOCK_CORRECTION: corrected_*）、(2) 同一期間の重複（ONL-005）、(3) 残日数 − PENDING 引当 ≧ 日数、(4) status と current_step の対応、(5) 提出時（ONL-005/022）に approval_steps を必ず 2 行作成（再提出は旧行を削除してから）、(6) 申請者本人は自分の申請を承認不可（E-009）。</t>
+          <t>整合性をアプリで守る点：(1) 種別別の必須項目（LEAVE: leave_type_id/unit/days、CLOCK_CORRECTION: corrected_clock_*、BREAK_CORRECTION: corrected_break_*。4.4・4.5）、(2) 同一期間の重複（ONL-005）、(3) 残日数 − PENDING 引当 ≧ 日数、(4) status と current_step の対応、(5) 提出時（ONL-005/022）に approval_steps を作成（上長ありは 2 行、上長なし・無効は 2段目のみ。再提出は旧行を削除してから）、(6) 申請者本人は自分の申請を承認不可（E-009）。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -6376,7 +7333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6391,6 +7348,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -6827,6 +7785,7 @@
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="10" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -8348,9 +9307,9 @@
   <mergeCells count="18">
     <mergeCell ref="D14:J14"/>
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D3:J3"/>
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D3:J3"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
@@ -8377,7 +9336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8388,6 +9347,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
@@ -8467,12 +9427,12 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>ロック順序</t>
+          <t>休憩・離席修正の最終承認（ONL-010）</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → notifications（ONL-005/022）、requests → approval_steps → leave_balances / attendance_records → notifications（ONL-010）。取下げ（ONL-008）は requests のみ。</t>
+          <t>requests（FOR UPDATE）→ approval_steps → attendance_records（FOR UPDATE。対象日の行）→ attendance_breaks。最終承認時にも checkBreakCorrection を再実行する（提出後に打刻された区間と重なる等）。違反（E-003／E-005）や承認者の操作が重なった場合は例外で全体がロールバックされ、ステップは WAITING のまま残る。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -8480,15 +9440,15 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>トランザクション注意</t>
+          <t>ロック順序</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>承認系は『ステップ更新・申請更新・消化/反映・通知』を 1 トランザクション。残日数不足（E-004）などで例外になると全てロールバックされ、ステップは WAITING のまま。</t>
+          <t>users → requests → approval_steps → notifications（ONL-005/022）、requests → approval_steps → leave_balances / attendance_records → notifications（ONL-010）。取下げ（ONL-008）は requests のみ。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -8496,61 +9456,54 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>トランザクション注意</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>承認系は『ステップ更新・申請更新・消化/反映・通知』を 1 トランザクション。残日数不足（E-004）などで例外になると全てロールバックされ、ステップは WAITING のまま。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>7.2 FOR UPDATE を使う処理（アクセスパターンから自動抽出）</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>処理名</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>SQL 区分</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ONL-008</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>申請取下げ</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>処理名</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>SQL 区分</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
@@ -8559,17 +9512,17 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>申請取下げ</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>申請取得・行ロック（RequestRepository#findByIdForUpdate）</t>
+          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8583,12 +9536,12 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ONL-011</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>差戻し</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -8607,12 +9560,12 @@
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>ONL-012</t>
+          <t>ONL-011</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>差戻し</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -8631,17 +9584,17 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-012</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>却下</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
+          <t>申請取得・行ロック（RequestRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -8652,43 +9605,52 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>7.3 共通前提</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>分離レベル</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
     </row>
-    <row r="20" ht="34" customHeight="1">
+    <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>ロック順序（デッドロック防止）</t>
+          <t>分離レベル</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
+          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -8696,15 +9658,15 @@
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>ロック待ち</t>
+          <t>ロック順序（デッドロック防止）</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>バッチは lock.timeout=5000ms（BAT-001 D-8）。オンラインは既定（待ち続ける）のためトランザクションを短く保つ。</t>
+          <t>users → requests → approval_steps → leave_balances / attendance_records → attendance_breaks → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一。休憩・離席の打刻 ONL-024/025 は attendance_records の行ロック → attendance_breaks）。</t>
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
@@ -8712,195 +9674,213 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>ロック待ち</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>バッチは lock.timeout=5000ms（BAT-001 D-8）。オンラインは既定（待ち続ける）のためトランザクションを短く保つ。</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>7.4 再提出（ONL-022）の SQL 手順：DRAFT / RETURNED → PENDING と approval_steps の作り直し（1 トランザクション）</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>申請者を行ロック</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>SELECT id FROM users WHERE email='taro@example.com' FOR UPDATE;</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="34" customHeight="1">
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>申請を行ロックし、DRAFT / RETURNED であることを確認（それ以外は E-016）</t>
+          <t>申請者を行ロック</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, status FROM requests WHERE id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION') FOR UPDATE;</t>
+          <t>SELECT id FROM users WHERE email='taro@example.com' FOR UPDATE;</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="63" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>申請を PENDING に更新（上長ありは current_step=1、上長なしは 2。LEAVE は days も再計算して SET。updated_at はトリガ）</t>
+          <t>申請を行ロックし、DRAFT / RETURNED であることを確認（それ以外は E-016）</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>UPDATE requests SET status='PENDING', current_step=1, submitted_at=TIMESTAMP '2026-10-03 10:00:00' WHERE id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION') AND status IN ('DRAFT','RETURNED');</t>
+          <t>SELECT id, status FROM requests WHERE id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION') FOR UPDATE;</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="63" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>旧承認ステップを全て削除（DRAFT は 0 件。差戻しコメントも消える）</t>
+          <t>申請を PENDING に更新（上長ありは current_step=1、上長なしは 2。LEAVE は days も再計算して SET。updated_at はトリガ）</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>DELETE FROM approval_steps WHERE request_id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION');</t>
+          <t>UPDATE requests SET status='PENDING', current_step=1, submitted_at=TIMESTAMP '2026-10-03 10:00:00' WHERE id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION') AND status IN ('DRAFT','RETURNED');</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="10" t="n"/>
     </row>
-    <row r="29" ht="77.5" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>承認ステップを作り直す（1段目＝再提出時点の上長、2段目＝NULL）</t>
+          <t>旧承認ステップを全て削除（DRAFT は 0 件。差戻しコメントも消える）</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO approval_steps(request_id,step_no,approver_id,status) VALUES ((SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),1,(SELECT manager_id FROM users WHERE email='taro@example.com'),'WAITING'),((SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),2,NULL,'WAITING');</t>
+          <t>DELETE FROM approval_steps WHERE request_id = (SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION');</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="48.5" customHeight="1">
+    <row r="30" ht="77.5" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>現在の承認者へ REQUEST_SUBMITTED を通知（request_id は更新後の申請 ID）</t>
+          <t>承認ステップを作り直す（1段目＝再提出時点の上長、2段目＝NULL）</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO notifications(user_id,type,request_id,message) VALUES ((SELECT manager_id FROM users WHERE email='taro@example.com'),'REQUEST_SUBMITTED',(SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),'山田 太郎さんから打刻修正申請（2026-09-30）が提出されました。');</t>
+          <t>INSERT INTO approval_steps(request_id,step_no,approver_id,status) VALUES ((SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),1,(SELECT manager_id FROM users WHERE email='taro@example.com'),'WAITING'),((SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),2,NULL,'WAITING');</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
     </row>
-    <row r="31" ht="34" customHeight="1">
+    <row r="31" ht="48.5" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>8章のデータ（申請 3：山田の打刻修正、RETURNED）を例にした手順。実行確認では BEGIN … ROLLBACK で検証した。条件付き UPDATE（WHERE status IN ('DRAFT','RETURNED')）を追加すれば行ロックに加えた二重の保証になるが、ONL-022 は FOR UPDATE 後にアプリ側で状態を判定している。</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>現在の承認者へ REQUEST_SUBMITTED を通知（request_id は更新後の申請 ID）</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO notifications(user_id,type,request_id,message) VALUES ((SELECT manager_id FROM users WHERE email='taro@example.com'),'REQUEST_SUBMITTED',(SELECT id FROM requests WHERE user_id=(SELECT id FROM users WHERE email='taro@example.com') AND start_date=DATE '2026-09-30' AND request_type='CLOCK_CORRECTION'),'山田 太郎さんから打刻修正申請（2026-09-30）が提出されました。');</t>
+        </is>
+      </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
     </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>8章のデータ（申請 3：山田の打刻修正、RETURNED）を例にした手順。実行確認では BEGIN … ROLLBACK で検証した。条件付き UPDATE（WHERE status IN ('DRAFT','RETURNED')）を追加すれば行ロックに加えた二重の保証になるが、ONL-022 は FOR UPDATE 後にアプリ側で状態を判定している。</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D13:F13"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B22:F22"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="B19:F19"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C25:F25"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B5:F5"/>
